--- a/preview/pr-13/ValueSet-dem-haeufigkeit-5-vs.xlsx
+++ b/preview/pr-13/ValueSet-dem-haeufigkeit-5-vs.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T07:34:58+00:00</t>
+    <t>2026-09-30T07:33:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -152,7 +152,7 @@
     <t>staendig</t>
   </si>
   <si>
-    <t>Ständig</t>
+    <t>Always</t>
   </si>
   <si>
     <t>false</t>
@@ -161,25 +161,25 @@
     <t>meistens</t>
   </si>
   <si>
-    <t>Meistens</t>
+    <t>Often</t>
   </si>
   <si>
     <t>manchmal</t>
   </si>
   <si>
-    <t>Manchmal</t>
+    <t>Sometimes</t>
   </si>
   <si>
     <t>selten</t>
   </si>
   <si>
-    <t>Selten</t>
+    <t>Rarely</t>
   </si>
   <si>
     <t>nie</t>
   </si>
   <si>
-    <t>Nie</t>
+    <t>Never</t>
   </si>
 </sst>
 </file>

--- a/preview/pr-13/ValueSet-dem-haeufigkeit-5-vs.xlsx
+++ b/preview/pr-13/ValueSet-dem-haeufigkeit-5-vs.xlsx
@@ -32,7 +32,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.0</t>
+    <t>0.3.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T07:33:31+00:00</t>
+    <t>2026-09-30T08:17:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/preview/pr-13/ValueSet-dem-haeufigkeit-5-vs.xlsx
+++ b/preview/pr-13/ValueSet-dem-haeufigkeit-5-vs.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T08:17:00+00:00</t>
+    <t>2026-09-30T08:27:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -122,7 +122,7 @@
     <t>used-codesystem</t>
   </si>
   <si>
-    <t>https://bih-cei.github.io/PCOR-MII/CodeSystem/dem-haeufigkeit-5|0.1.0</t>
+    <t>https://bih-cei.github.io/PCOR-MII/CodeSystem/dem-haeufigkeit-5|0.3.0</t>
   </si>
   <si>
     <t>Level</t>
